--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/BHNVFEAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA20C4-17B7-544F-8110-ED0EE48F65C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1FB9D6-4259-754A-82F0-60B2DEE83256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -8100,13 +8100,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -8203,8 +8203,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -8332,10 +8392,88 @@
         <f t="shared" si="0"/>
         <v>3.3390253679910294E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="1">AG2</f>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3390253679910294E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -8343,67 +8481,67 @@
         <v>0</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:R8" si="1">B3</f>
+        <f t="shared" ref="C3:R8" si="2">B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S3" s="4">
@@ -8462,10 +8600,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="3">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8473,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -8592,10 +8808,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
+      <c r="AG4" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -8603,7 +8897,7 @@
         <v>3.5041036558001674E-3</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.5041036558001674E-3</v>
       </c>
       <c r="D5" s="4">
@@ -8722,10 +9016,88 @@
         <f t="shared" si="0"/>
         <v>3.5041036558001674E-3</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="3"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5041036558001674E-3</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8733,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D6" s="4">
@@ -8852,10 +9224,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
+      <c r="AG6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -8863,7 +9313,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -8982,10 +9432,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="AG7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -8993,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -9112,8 +9640,86 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9125,13 +9731,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -9228,8 +9834,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9357,10 +10023,88 @@
         <f>AF$5/(1-'Other Values'!$B$3)</f>
         <v>1.5806683889015623E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5806683889015623E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9457,8 +10201,88 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -9555,8 +10379,88 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -9684,10 +10588,88 @@
         <f>Extrapolations!AT6</f>
         <v>4.9188761878420821E-4</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -9784,8 +10766,88 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -9882,8 +10944,88 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -10011,8 +11153,86 @@
         <f>AF$5*Calculations!$B$27</f>
         <v>1.4756628563526244E-3</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10024,13 +11244,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -10127,8 +11347,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -10256,10 +11536,88 @@
         <f>AF$5/(1-'Other Values'!$B$3)</f>
         <v>4.069763563679482E-4</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>4.069763563679482E-4</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -10356,8 +11714,88 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10454,8 +11892,88 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -10583,10 +12101,88 @@
         <f>Extrapolations!AT7</f>
         <v>1.2664682373664536E-4</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2664682373664536E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -10683,8 +12279,88 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -10781,8 +12457,88 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -10910,8 +12666,86 @@
         <f>AF$5*Calculations!$B$27</f>
         <v>3.7994047120993603E-4</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7994047120993603E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10923,7 +12757,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
@@ -10931,7 +12765,7 @@
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -11028,8 +12862,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -11157,10 +13051,88 @@
         <f>Extrapolations!AJ9</f>
         <v>1.2512344612634041E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2512344612634041E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -11257,8 +13229,88 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -11355,8 +13407,88 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -11484,10 +13616,88 @@
         <f>Extrapolations!AT6</f>
         <v>4.9188761878420821E-4</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9188761878420821E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -11584,8 +13794,88 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -11682,8 +13972,88 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -11811,10 +14181,88 @@
         <f>AF$5*Calculations!$B$27</f>
         <v>1.4756628563526244E-3</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4756628563526244E-3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:52">
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
@@ -11858,13 +14306,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -11961,8 +14409,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -12090,10 +14598,88 @@
         <f>AF$5/(1-'Other Values'!$B$3)</f>
         <v>1.0856384124632192E-2</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0856384124632192E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12190,8 +14776,88 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -12288,8 +14954,88 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -12417,10 +15163,88 @@
         <f>Extrapolations!AJ10</f>
         <v>3.3783942116935514E-3</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3783942116935514E-3</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -12517,8 +15341,88 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -12615,8 +15519,88 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -12744,8 +15728,86 @@
         <f>AF$5*Calculations!$B$27</f>
         <v>1.0135182635080653E-2</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0135182635080653E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12757,14 +15819,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -12861,8 +15923,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -12990,10 +16112,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="1">AG2</f>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -13001,67 +16201,67 @@
         <v>0</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:R8" si="1">B3</f>
+        <f t="shared" ref="C3:R8" si="2">B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S3" s="4">
@@ -13120,8 +16320,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="3">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -13129,7 +16409,7 @@
         <v>2.2779143897302514E-4</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2779143897302514E-4</v>
       </c>
       <c r="D4" s="4">
@@ -13248,8 +16528,88 @@
         <f t="shared" si="0"/>
         <v>2.2779143897302514E-4</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="3"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2779143897302514E-4</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -13257,7 +16617,7 @@
         <v>8.5088222715209791E-8</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.5088222715209791E-8</v>
       </c>
       <c r="D5" s="4">
@@ -13376,10 +16736,88 @@
         <f t="shared" si="0"/>
         <v>8.5088222715209791E-8</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="3"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5088222715209791E-8</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -13387,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D6" s="4">
@@ -13506,8 +16944,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -13515,7 +17033,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -13634,8 +17152,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -13643,7 +17241,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -13762,8 +17360,86 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13775,13 +17451,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -13878,8 +17554,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -14007,10 +17743,88 @@
         <f>AF$5/(1-'Other Values'!$B$3)</f>
         <v>1.5975871779246587E-2</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5975871779246587E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -14107,8 +17921,88 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14205,8 +18099,88 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -14334,10 +18308,88 @@
         <f>Extrapolations!AK12</f>
         <v>4.971525705626559E-3</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.971525705626559E-3</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -14434,8 +18486,88 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -14532,8 +18664,88 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -14661,8 +18873,86 @@
         <f>AF$5*Calculations!$B$27</f>
         <v>1.4914577116879674E-2</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.4914577116879674E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14674,13 +18964,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -14777,8 +19067,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -14906,10 +19256,88 @@
         <f t="shared" si="0"/>
         <v>9.8648567589705791E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="1">AG2</f>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8648567589705791E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -14917,67 +19345,67 @@
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:R8" si="1">B3</f>
+        <f t="shared" ref="C3:R8" si="2">B3</f>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2056566177618372E-3</v>
       </c>
       <c r="S3" s="4">
@@ -15036,10 +19464,88 @@
         <f t="shared" si="0"/>
         <v>1.2056566177618372E-3</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="3">AF3</f>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2056566177618372E-3</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15047,7 +19553,7 @@
         <v>1.1311305355858213E-3</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1311305355858213E-3</v>
       </c>
       <c r="D4" s="4">
@@ -15166,10 +19672,88 @@
         <f t="shared" si="0"/>
         <v>1.1311305355858213E-3</v>
       </c>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
+      <c r="AG4" s="4">
+        <f t="shared" si="3"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1311305355858213E-3</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -15177,7 +19761,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D5" s="4">
@@ -15296,10 +19880,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -15307,7 +19969,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D6" s="4">
@@ -15426,10 +20088,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
+      <c r="AG6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -15437,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -15556,10 +20296,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="AG7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -15567,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -15686,8 +20504,86 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15699,13 +20595,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:BA8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="16">
+    <row r="1" spans="1:53" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -15805,8 +20701,68 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1">
+        <v>2051</v>
+      </c>
+      <c r="AI1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1">
+        <v>2053</v>
+      </c>
+      <c r="AK1">
+        <v>2054</v>
+      </c>
+      <c r="AL1">
+        <v>2055</v>
+      </c>
+      <c r="AM1">
+        <v>2056</v>
+      </c>
+      <c r="AN1">
+        <v>2057</v>
+      </c>
+      <c r="AO1">
+        <v>2058</v>
+      </c>
+      <c r="AP1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1">
+        <v>2060</v>
+      </c>
+      <c r="AR1">
+        <v>2061</v>
+      </c>
+      <c r="AS1">
+        <v>2062</v>
+      </c>
+      <c r="AT1">
+        <v>2063</v>
+      </c>
+      <c r="AU1">
+        <v>2064</v>
+      </c>
+      <c r="AV1">
+        <v>2065</v>
+      </c>
+      <c r="AW1">
+        <v>2066</v>
+      </c>
+      <c r="AX1">
+        <v>2067</v>
+      </c>
+      <c r="AY1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1">
+        <v>2069</v>
+      </c>
+      <c r="BA1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:53">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15906,8 +20862,88 @@
       <c r="AG2">
         <v>0</v>
       </c>
+      <c r="AH2" s="4">
+        <f>AG2</f>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" ref="AI2:BA8" si="0">AH2</f>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:53">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -16007,8 +21043,88 @@
       <c r="AG3">
         <v>0</v>
       </c>
+      <c r="AH3" s="4">
+        <f t="shared" ref="AH3:AW8" si="1">AG3</f>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:53">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16108,8 +21224,88 @@
       <c r="AG4">
         <v>0</v>
       </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:53">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -16209,8 +21405,88 @@
       <c r="AG5">
         <v>0</v>
       </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:53">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -16310,8 +21586,88 @@
       <c r="AG6">
         <v>0</v>
       </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:53">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -16411,8 +21767,88 @@
       <c r="AG7">
         <v>0</v>
       </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:53">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -16510,6 +21946,86 @@
         <v>0</v>
       </c>
       <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -23091,13 +28607,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -23194,8 +28710,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -23323,10 +28899,88 @@
         <f>SYFAFE!$B$2</f>
         <v>3.8548169292405357E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="0">AG2</f>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8548169292405357E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -23454,10 +29108,88 @@
         <f>BNVFE!AF25*('BHNVFEAL-LDVs-psgr'!AF$4/BNVFE!AF$26)</f>
         <v>4.3506172517354685E-4</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="1">AF3</f>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="0"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="0"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>4.3506172517354685E-4</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -23585,10 +29317,88 @@
         <f>Extrapolations!BE2</f>
         <v>4.6479081055883617E-4</v>
       </c>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
+      <c r="AG4" s="4">
+        <f t="shared" si="1"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="0"/>
+        <v>4.6479081055883617E-4</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -23716,10 +29526,88 @@
         <f>BNVFE!AF27*('BHNVFEAL-LDVs-psgr'!AF$4/BNVFE!AF$26)</f>
         <v>4.5870472030867576E-4</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="1"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5870472030867576E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -23847,10 +29735,88 @@
         <f>BNVFE!AF28*('BHNVFEAL-LDVs-psgr'!AF$4/BNVFE!AF$26)</f>
         <v>7.6990379444637376E-4</v>
       </c>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
+      <c r="AG6" s="4">
+        <f t="shared" si="1"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.6990379444637376E-4</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -23978,10 +29944,88 @@
         <f>BNVFE!AF29*('BHNVFEAL-LDVs-psgr'!AF$4/BNVFE!AF$26)</f>
         <v>4.1109763007020822E-4</v>
       </c>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="AG7" s="4">
+        <f t="shared" si="1"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.1109763007020822E-4</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -23994,125 +30038,203 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:AF8" si="0">C8</f>
+        <f t="shared" ref="D8:AF8" si="2">C8</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF8" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:52">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -24157,13 +30279,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -24260,8 +30382,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -24389,10 +30571,88 @@
         <f t="shared" si="0"/>
         <v>4.8694119949868023E-4</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="1">AG2</f>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8694119949868023E-4</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -24400,67 +30660,67 @@
         <v>0</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:R8" si="1">B3</f>
+        <f t="shared" ref="C3:R8" si="2">B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S3" s="4">
@@ -24519,10 +30779,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="3">AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -24530,7 +30868,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -24649,10 +30987,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
+      <c r="AG4" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -24660,7 +31076,7 @@
         <v>5.110151164708477E-4</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.110151164708477E-4</v>
       </c>
       <c r="D5" s="4">
@@ -24779,10 +31195,88 @@
         <f t="shared" si="0"/>
         <v>5.110151164708477E-4</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="3"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="1"/>
+        <v>5.110151164708477E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -24790,7 +31284,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D6" s="4">
@@ -24909,10 +31403,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
+      <c r="AG6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -24920,7 +31492,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -25039,10 +31611,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="AG7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -25050,7 +31700,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -25169,8 +31819,86 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25182,13 +31910,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16">
+    <row r="1" spans="1:52" ht="16">
       <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
@@ -25285,8 +32013,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -25414,10 +32202,88 @@
         <f t="shared" si="0"/>
         <v>5.8893036418951787E-3</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
+      <c r="AG2" s="4">
+        <f>AF2</f>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AZ8" si="1">AG2</f>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AI2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="1"/>
+        <v>5.8893036418951787E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -25425,67 +32291,67 @@
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:R8" si="1">B3</f>
+        <f t="shared" ref="C3:R8" si="2">B3</f>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2411171065195511E-3</v>
       </c>
       <c r="S3" s="4">
@@ -25544,10 +32410,88 @@
         <f t="shared" si="0"/>
         <v>1.2411171065195511E-3</v>
       </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
+      <c r="AG3" s="4">
+        <f t="shared" ref="AG3:AV8" si="3">AF3</f>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AH3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AI3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AK3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AL3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AN3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AP3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AS3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AT3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AU3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AV3" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2411171065195511E-3</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -25555,7 +32499,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -25674,10 +32618,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
+      <c r="AG4" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -25685,7 +32707,7 @@
         <v>1.0956176988720018E-3</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0956176988720018E-3</v>
       </c>
       <c r="D5" s="4">
@@ -25804,10 +32826,88 @@
         <f t="shared" si="0"/>
         <v>1.0956176988720018E-3</v>
       </c>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
+      <c r="AG5" s="4">
+        <f t="shared" si="3"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AH5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AI5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AN5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AO5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AQ5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AR5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AS5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AT5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AU5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AV5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AW5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AX5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AY5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.0956176988720018E-3</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -25815,7 +32915,7 @@
         <v>1.1497840120594071E-3</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1497840120594071E-3</v>
       </c>
       <c r="D6" s="4">
@@ -25934,10 +33034,88 @@
         <f t="shared" si="0"/>
         <v>1.1497840120594071E-3</v>
       </c>
-      <c r="AH6" s="4"/>
-      <c r="AI6" s="4"/>
+      <c r="AG6" s="4">
+        <f t="shared" si="3"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AH6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AI6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AN6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AO6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AQ6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AS6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AT6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AU6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AV6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1497840120594071E-3</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -25945,7 +33123,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -26064,10 +33242,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="AG7" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -26075,7 +33331,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -26194,8 +33450,86 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
+      <c r="AG8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
